--- a/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
+++ b/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
@@ -459,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1077,15 +1076,15 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
-        <v>85</v>
+      <c r="D34" t="n">
+        <v>7</v>
       </c>
       <c r="F34" t="n">
         <v>0.44</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 87 at dist 0.1077</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 87 at dist 0.1077)</t>
         </is>
       </c>
     </row>
@@ -1093,15 +1092,15 @@
       <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
-        <v>87</v>
+      <c r="D35" t="n">
+        <v>9</v>
       </c>
       <c r="F35" t="n">
         <v>0.964</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>702 verts (Body) -&gt; 173 verts (Head), dist 0.2631; runner-up 23 at dist 0.2112</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2631; runner-up 23 at dist 0.2112)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1116,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 23 at dist 0.2687</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 23 at dist 0.2687)</t>
         </is>
       </c>
     </row>
@@ -1125,15 +1124,15 @@
       <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
-        <v>85</v>
+      <c r="D37" t="n">
+        <v>7</v>
       </c>
       <c r="F37" t="n">
         <v>0.494</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 70 at dist 0.1273</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 70 at dist 0.1273)</t>
         </is>
       </c>
     </row>
@@ -1141,15 +1140,15 @@
       <c r="A38" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
-        <v>87</v>
+      <c r="D38" t="n">
+        <v>9</v>
       </c>
       <c r="F38" t="n">
         <v>0.667</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:7 at dist 0.1508</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:7 at dist 0.1508)</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1164,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:9 at dist 0.2280</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:9 at dist 0.2280)</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1180,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:21 at dist 0.3067</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:21 at dist 0.3067)</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1196,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Reviewed: tip of the long back coat tail (cyan trim); the skin coat's tail end, not the skin's CALF (cloth onto a leg). Tool proposed 6. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:24 at dist 0.3440)</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail (cyan trim); the skin coat's tail end, not the skin's CALF (cloth onto a leg). Tool proposed 6. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:24 at dist 0.3440))</t>
         </is>
       </c>
     </row>
@@ -1205,15 +1204,15 @@
       <c r="A42" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
-        <v>86</v>
+      <c r="D42" t="n">
+        <v>8</v>
       </c>
       <c r="F42" t="n">
         <v>0.439</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 88 at dist 0.1077</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 88 at dist 0.1077)</t>
         </is>
       </c>
     </row>
@@ -1221,15 +1220,15 @@
       <c r="A43" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
-        <v>88</v>
+      <c r="D43" t="n">
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>0.962</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>702 verts (Body) -&gt; 173 verts (Head), dist 0.2630; runner-up 43 at dist 0.2113</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2630; runner-up 43 at dist 0.2113)</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1244,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 43 at dist 0.2687</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 43 at dist 0.2687)</t>
         </is>
       </c>
     </row>
@@ -1253,15 +1252,15 @@
       <c r="A45" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
-        <v>86</v>
+      <c r="D45" t="n">
+        <v>8</v>
       </c>
       <c r="F45" t="n">
         <v>0.405</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 71 at dist 0.1310</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 71 at dist 0.1310)</t>
         </is>
       </c>
     </row>
@@ -1269,15 +1268,15 @@
       <c r="A46" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
-        <v>88</v>
+      <c r="D46" t="n">
+        <v>10</v>
       </c>
       <c r="F46" t="n">
         <v>0.576</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:8 at dist 0.1616</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:8 at dist 0.1616)</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1292,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:10 at dist 0.2280</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:10 at dist 0.2280)</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1308,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:22 at dist 0.3067</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:22 at dist 0.3067)</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1324,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Reviewed: tip of the long back coat tail, right; the skin coat's tail end, not the calf. Tool proposed 26. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:25 at dist 0.3440)</t>
+          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail, right; the skin coat's tail end, not the calf. Tool proposed 26. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:25 at dist 0.3440))</t>
         </is>
       </c>
     </row>
@@ -3324,14 +3323,14 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C55" t="n">
         <v>0.872</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Reviewed: the skin's left sleeve cuff (forward 58 -&gt; 53); Neuvillette's cuff bone rather than a THUMB bone (111). Tool proposed 111. (220 verts (Head) -&gt; 103 verts (Body/Dress), dist 0.1007; runner-up 112 at dist 0.1332)</t>
+          <t>Reviewed (in game, 2026-09-25): the main mesh's cuff band onto his FOREARM (85 / 104, the bone his hand chain shares vertices with), not his separate cuff piece (58 / 61). (was: Reviewed: the skin's left sleeve cuff (forward 58 -&gt; 53); Neuvillette's cuff bone rather than a THUMB bone (111). Tool proposed 111. (220 verts (Head) -&gt; 103 verts (Body/Dress), dist 0.1007; runner-up 112 at dist 0.1332))</t>
         </is>
       </c>
     </row>
@@ -3340,14 +3339,14 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="C56" t="n">
         <v>0.698</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Reviewed: the skin's right sleeve cuff; Neuvillette's cuff bone rather than a thumb bone (113). Tool proposed 113. (218 verts (Head) -&gt; 155 verts (Body/Dress), dist 0.0733; runner-up 104 at dist 0.0706)</t>
+          <t>Reviewed (in game, 2026-09-25): the main mesh's cuff band onto his FOREARM (85 / 104, the bone his hand chain shares vertices with), not his separate cuff piece (58 / 61). (was: Reviewed: the skin's right sleeve cuff; Neuvillette's cuff bone rather than a thumb bone (113). Tool proposed 113. (218 verts (Head) -&gt; 155 verts (Body/Dress), dist 0.0733; runner-up 104 at dist 0.0706))</t>
         </is>
       </c>
     </row>
@@ -4438,14 +4437,14 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" t="n">
         <v>0.37</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>366 verts (A) -&gt; 163 verts (Body), dist 0.0650; runner-up 66 at dist 0.1276; in chain Coat:13-14 -&gt; 64-65</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the mantle's RIGHT shoulder onto 67, the mirror of its left twin's 64 (the draft had 65). (was: 366 verts (A) -&gt; 163 verts (Body), dist 0.0650; runner-up 66 at dist 0.1276; in chain Coat:13-14 -&gt; 64-65)</t>
         </is>
       </c>
     </row>
@@ -4710,14 +4709,14 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C33" t="n">
         <v>0.483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>231 verts (A) -&gt; 163 verts (Body), dist 0.1051; runner-up 19 at dist 0.1795; in chain Coat:30-31 -&gt; 64-65</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the mantle's RIGHT shoulder onto 67, the mirror of its left twin's 64 (the draft had 65). (was: 231 verts (A) -&gt; 163 verts (Body), dist 0.1051; runner-up 19 at dist 0.1795; in chain Coat:30-31 -&gt; 64-65)</t>
         </is>
       </c>
     </row>
@@ -4726,14 +4725,14 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C34" t="n">
         <v>0.766</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Reviewed: coat's left UPPER SLEEVE (it runs down the arm in the front view); Neuvillette's upper-sleeve bone, not HAIR (20) -- cloth riding hair wobbles. Tool proposed 20. (308 verts (A) -&gt; 175 verts (Head), dist 0.0888; runner-up 57 at dist 0.1112)</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the skin wears its coat as a MANTLE, its sleeves hanging empty behind the arms on a chain of their own; the whole chain onto his UPPER ARM (64 / 67). On his cuff piece and shoulder cloth the cuff jutted out at elbow height; on his clavicle the sleeves flared out at idle. (was: Reviewed: coat's left UPPER SLEEVE (it runs down the arm in the front view); Neuvillette's upper-sleeve bone, not HAIR (20) -- cloth riding hair wobbles. Tool proposed 20. (308 verts (A) -&gt; 175 verts (Head), dist 0.0888; runner-up 57 at dist 0.1112))</t>
         </is>
       </c>
     </row>
@@ -4742,14 +4741,14 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C35" t="n">
         <v>0.727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reviewed: coat's right upper sleeve; Neuvillette's upper-sleeve bone, not HAIR (19). Tool proposed 19. (308 verts (A) -&gt; 175 verts (Head), dist 0.0888; runner-up 60 at dist 0.1112; in chain Coat:33-34 -&gt; 19-20)</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the skin wears its coat as a MANTLE, its sleeves hanging empty behind the arms on a chain of their own; the whole chain onto his UPPER ARM (64 / 67). On his cuff piece and shoulder cloth the cuff jutted out at elbow height; on his clavicle the sleeves flared out at idle. (was: Reviewed: coat's right upper sleeve; Neuvillette's upper-sleeve bone, not HAIR (19). Tool proposed 19. (308 verts (A) -&gt; 175 verts (Head), dist 0.0888; runner-up 60 at dist 0.1112; in chain Coat:33-34 -&gt; 19-20))</t>
         </is>
       </c>
     </row>
@@ -4758,14 +4757,14 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C36" t="n">
         <v>0.949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reviewed: coat sleeve, left, hanging behind the arm; Neuvillette's sleeve cuff (vertices mode), not HAIR (20). Tool proposed 20. (1452 verts (A) -&gt; 175 verts (Head), dist 0.2955; runner-up 58 at dist 0.2158; in chain Coat:33-34 -&gt; 19-20)</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the skin wears its coat as a MANTLE, its sleeves hanging empty behind the arms on a chain of their own; the whole chain onto his UPPER ARM (64 / 67). On his cuff piece and shoulder cloth the cuff jutted out at elbow height; on his clavicle the sleeves flared out at idle. (was: Reviewed: coat sleeve, left, hanging behind the arm; Neuvillette's sleeve cuff (vertices mode), not HAIR (20). Tool proposed 20. (1452 verts (A) -&gt; 175 verts (Head), dist 0.2955; runner-up 58 at dist 0.2158; in chain Coat:33-34 -&gt; 19-20))</t>
         </is>
       </c>
     </row>
@@ -4774,14 +4773,14 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C37" t="n">
         <v>0.621</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1452 verts (A) -&gt; 733 verts (Body), dist 0.2158; runner-up 99 at dist 0.2560</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the skin wears its coat as a MANTLE, its sleeves hanging empty behind the arms on a chain of their own; the whole chain onto his UPPER ARM (64 / 67). On his cuff piece and shoulder cloth the cuff jutted out at elbow height; on his clavicle the sleeves flared out at idle. (was: 1452 verts (A) -&gt; 733 verts (Body), dist 0.2158; runner-up 99 at dist 0.2560)</t>
         </is>
       </c>
     </row>
@@ -4790,14 +4789,14 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C38" t="n">
         <v>0.9340000000000001</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Reviewed: coat sleeve, left, lower; the sleeve cuff (vertices mode), not a FINGER bone (82). Tool proposed 82. (1639 verts (A) -&gt; 53 verts (Body), dist 0.2577; runner-up 81 at dist 0.2635)</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the skin wears its coat as a MANTLE, its sleeves hanging empty behind the arms on a chain of their own; the whole chain onto his UPPER ARM (64 / 67). On his cuff piece and shoulder cloth the cuff jutted out at elbow height; on his clavicle the sleeves flared out at idle. (was: Reviewed: coat sleeve, left, lower; the sleeve cuff (vertices mode), not a FINGER bone (82). Tool proposed 82. (1639 verts (A) -&gt; 53 verts (Body), dist 0.2577; runner-up 81 at dist 0.2635))</t>
         </is>
       </c>
     </row>
@@ -4806,14 +4805,14 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C39" t="n">
         <v>0.9340000000000001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Reviewed: coat sleeve, right, lower; the sleeve cuff (vertices mode), not a FINGER bone (101). Tool proposed 101. (1639 verts (A) -&gt; 53 verts (Body), dist 0.2577; runner-up 100 at dist 0.2635)</t>
+          <t>Reviewed (in game, the identity mod, 2026-09-25): the skin wears its coat as a MANTLE, its sleeves hanging empty behind the arms on a chain of their own; the whole chain onto his UPPER ARM (64 / 67). On his cuff piece and shoulder cloth the cuff jutted out at elbow height; on his clavicle the sleeves flared out at idle. (was: Reviewed: coat sleeve, right, lower; the sleeve cuff (vertices mode), not a FINGER bone (101). Tool proposed 101. (1639 verts (A) -&gt; 53 verts (Body), dist 0.2577; runner-up 100 at dist 0.2635))</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
+++ b/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
@@ -564,15 +564,15 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>3</v>
+      <c r="B2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0.384</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>379 verts (Body/Dress) -&gt; 477 verts (A), dist 0.0737; runner-up Coat:2 at dist 0.1252; in chain 0-1 -&gt; Coat:3-4</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: 379 verts (Body/Dress) -&gt; 477 verts (A), dist 0.0737; runner-up Coat:2 at dist 0.1252; in chain 0-1 -&gt; Coat:3-4</t>
         </is>
       </c>
     </row>
@@ -580,15 +580,15 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>4</v>
+      <c r="B3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0.181</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>379 verts (Body/Dress) -&gt; 479 verts (A), dist 0.0736; runner-up Coat:2 at dist 0.1252; in chain 0-1 -&gt; Coat:3-4</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: 379 verts (Body/Dress) -&gt; 479 verts (A), dist 0.0736; runner-up Coat:2 at dist 0.1252; in chain 0-1 -&gt; Coat:3-4</t>
         </is>
       </c>
     </row>
@@ -1076,15 +1076,15 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="D34" t="n">
-        <v>7</v>
+      <c r="B34" t="n">
+        <v>85</v>
       </c>
       <c r="F34" t="n">
         <v>0.44</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 87 at dist 0.1077)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 87 at dist 0.1077)</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1092,15 @@
       <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="D35" t="n">
-        <v>9</v>
+      <c r="B35" t="n">
+        <v>23</v>
       </c>
       <c r="F35" t="n">
         <v>0.964</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2631; runner-up 23 at dist 0.2112)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2631; runner-up 23 at dist 0.2112)</t>
         </is>
       </c>
     </row>
@@ -1108,15 +1108,15 @@
       <c r="A36" t="n">
         <v>34</v>
       </c>
-      <c r="D36" t="n">
-        <v>24</v>
+      <c r="B36" t="n">
+        <v>23</v>
       </c>
       <c r="F36" t="n">
         <v>0.5580000000000001</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 23 at dist 0.2687)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 23 at dist 0.2687)</t>
         </is>
       </c>
     </row>
@@ -1124,15 +1124,15 @@
       <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="D37" t="n">
-        <v>7</v>
+      <c r="B37" t="n">
+        <v>73</v>
       </c>
       <c r="F37" t="n">
         <v>0.494</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 70 at dist 0.1273)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 70 at dist 0.1273)</t>
         </is>
       </c>
     </row>
@@ -1140,15 +1140,15 @@
       <c r="A38" t="n">
         <v>36</v>
       </c>
-      <c r="D38" t="n">
-        <v>9</v>
+      <c r="B38" t="n">
+        <v>87</v>
       </c>
       <c r="F38" t="n">
         <v>0.667</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:7 at dist 0.1508)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:7 at dist 0.1508)</t>
         </is>
       </c>
     </row>
@@ -1156,15 +1156,15 @@
       <c r="A39" t="n">
         <v>37</v>
       </c>
-      <c r="D39" t="n">
-        <v>24</v>
+      <c r="B39" t="n">
+        <v>23</v>
       </c>
       <c r="F39" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:9 at dist 0.2280)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:9 at dist 0.2280)</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1172,15 @@
       <c r="A40" t="n">
         <v>38</v>
       </c>
-      <c r="D40" t="n">
-        <v>24</v>
+      <c r="B40" t="n">
+        <v>6</v>
       </c>
       <c r="F40" t="n">
         <v>0.294</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:21 at dist 0.3067)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:21 at dist 0.3067)</t>
         </is>
       </c>
     </row>
@@ -1188,15 +1188,15 @@
       <c r="A41" t="n">
         <v>39</v>
       </c>
-      <c r="D41" t="n">
-        <v>24</v>
+      <c r="B41" t="n">
+        <v>6</v>
       </c>
       <c r="F41" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail (cyan trim); the skin coat's tail end, not the skin's CALF (cloth onto a leg). Tool proposed 6. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:24 at dist 0.3440))</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail (cyan trim); the skin coat's tail end, not the skin's CALF (cloth onto a leg). Tool proposed 6. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:24 at dist 0.3440))</t>
         </is>
       </c>
     </row>
@@ -1204,15 +1204,15 @@
       <c r="A42" t="n">
         <v>40</v>
       </c>
-      <c r="D42" t="n">
-        <v>8</v>
+      <c r="B42" t="n">
+        <v>86</v>
       </c>
       <c r="F42" t="n">
         <v>0.439</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 88 at dist 0.1077)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 88 at dist 0.1077)</t>
         </is>
       </c>
     </row>
@@ -1220,15 +1220,15 @@
       <c r="A43" t="n">
         <v>41</v>
       </c>
-      <c r="D43" t="n">
-        <v>10</v>
+      <c r="B43" t="n">
+        <v>43</v>
       </c>
       <c r="F43" t="n">
         <v>0.962</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2630; runner-up 43 at dist 0.2113)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2630; runner-up 43 at dist 0.2113)</t>
         </is>
       </c>
     </row>
@@ -1236,15 +1236,15 @@
       <c r="A44" t="n">
         <v>42</v>
       </c>
-      <c r="D44" t="n">
-        <v>25</v>
+      <c r="B44" t="n">
+        <v>43</v>
       </c>
       <c r="F44" t="n">
         <v>0.5580000000000001</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 43 at dist 0.2687)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 43 at dist 0.2687)</t>
         </is>
       </c>
     </row>
@@ -1252,15 +1252,15 @@
       <c r="A45" t="n">
         <v>43</v>
       </c>
-      <c r="D45" t="n">
-        <v>8</v>
+      <c r="B45" t="n">
+        <v>86</v>
       </c>
       <c r="F45" t="n">
         <v>0.405</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 71 at dist 0.1310)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 71 at dist 0.1310)</t>
         </is>
       </c>
     </row>
@@ -1268,15 +1268,15 @@
       <c r="A46" t="n">
         <v>44</v>
       </c>
-      <c r="D46" t="n">
-        <v>10</v>
+      <c r="B46" t="n">
+        <v>88</v>
       </c>
       <c r="F46" t="n">
         <v>0.576</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:8 at dist 0.1616)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:8 at dist 0.1616)</t>
         </is>
       </c>
     </row>
@@ -1284,15 +1284,15 @@
       <c r="A47" t="n">
         <v>45</v>
       </c>
-      <c r="D47" t="n">
-        <v>25</v>
+      <c r="B47" t="n">
+        <v>43</v>
       </c>
       <c r="F47" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:10 at dist 0.2280)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:10 at dist 0.2280)</t>
         </is>
       </c>
     </row>
@@ -1300,15 +1300,15 @@
       <c r="A48" t="n">
         <v>46</v>
       </c>
-      <c r="D48" t="n">
-        <v>25</v>
+      <c r="B48" t="n">
+        <v>26</v>
       </c>
       <c r="F48" t="n">
         <v>0.373</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:22 at dist 0.3067)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:22 at dist 0.3067)</t>
         </is>
       </c>
     </row>
@@ -1316,15 +1316,15 @@
       <c r="A49" t="n">
         <v>47</v>
       </c>
-      <c r="D49" t="n">
-        <v>25</v>
+      <c r="B49" t="n">
+        <v>26</v>
       </c>
       <c r="F49" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail, right; the skin coat's tail end, not the calf. Tool proposed 26. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:25 at dist 0.3440))</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail, right; the skin coat's tail end, not the calf. Tool proposed 26. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:25 at dist 0.3440))</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
+++ b/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
@@ -1093,14 +1093,14 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0.964</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2631; runner-up 23 at dist 0.2112)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2631; runner-up 23 at dist 0.2112)</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1109,14 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0.5580000000000001</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 23 at dist 0.2687)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 23 at dist 0.2687)</t>
         </is>
       </c>
     </row>
@@ -1157,14 +1157,14 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:9 at dist 0.2280)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:9 at dist 0.2280)</t>
         </is>
       </c>
     </row>
@@ -1173,14 +1173,14 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0.294</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:21 at dist 0.3067)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:21 at dist 0.3067)</t>
         </is>
       </c>
     </row>
@@ -1189,14 +1189,14 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail (cyan trim); the skin coat's tail end, not the skin's CALF (cloth onto a leg). Tool proposed 6. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:24 at dist 0.3440))</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail (cyan trim); the skin coat's tail end, not the skin's CALF (cloth onto a leg). Tool proposed 6. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:24 at dist 0.3440))</t>
         </is>
       </c>
     </row>
@@ -1221,14 +1221,14 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0.962</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2630; runner-up 43 at dist 0.2113)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 702 verts (Body) -&gt; 173 verts (Head), dist 0.2630; runner-up 43 at dist 0.2113)</t>
         </is>
       </c>
     </row>
@@ -1237,14 +1237,14 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0.5580000000000001</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 43 at dist 0.2687)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 630 verts (Body) -&gt; 109 verts (A), dist 0.2263; runner-up 43 at dist 0.2687)</t>
         </is>
       </c>
     </row>
@@ -1285,14 +1285,14 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:10 at dist 0.2280)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 225 verts (Body) -&gt; 109 verts (A), dist 0.2009; runner-up Coat:10 at dist 0.2280)</t>
         </is>
       </c>
     </row>
@@ -1301,14 +1301,14 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0.373</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:22 at dist 0.3067)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 220 verts (Body) -&gt; 109 verts (A), dist 0.2176; runner-up Coat:22 at dist 0.3067)</t>
         </is>
       </c>
     </row>
@@ -1317,14 +1317,14 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail, right; the skin coat's tail end, not the calf. Tool proposed 26. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:25 at dist 0.3440))</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on the PELVIS (knees/shins swung the hem with the idle pose), 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: Reviewed: tip of the long back coat tail, right; the skin coat's tail end, not the calf. Tool proposed 26. (173 verts (Body) -&gt; 1106 verts (Body), dist 0.3287; runner-up Coat:25 at dist 0.3440))</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
+++ b/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
@@ -1077,14 +1077,14 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0.44</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 87 at dist 0.1077)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on the PELVIS too (back-skirt bones folded Neuvillette3's flap), lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 87 at dist 0.1077)</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1125,14 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0.494</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 70 at dist 0.1273)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on the PELVIS too (back-skirt bones folded Neuvillette3's flap), lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 70 at dist 0.1273)</t>
         </is>
       </c>
     </row>
@@ -1141,14 +1141,14 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0.667</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:7 at dist 0.1508)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on the PELVIS too (back-skirt bones folded Neuvillette3's flap), lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:7 at dist 0.1508)</t>
         </is>
       </c>
     </row>
@@ -1205,14 +1205,14 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0.439</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 88 at dist 0.1077)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on the PELVIS too (back-skirt bones folded Neuvillette3's flap), lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 204 verts (Body) -&gt; 178 verts (Head), dist 0.0507; runner-up 88 at dist 0.1077)</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1253,14 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0.405</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 71 at dist 0.1310)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on the PELVIS too (back-skirt bones folded Neuvillette3's flap), lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 155 verts (Body) -&gt; 178 verts (Head), dist 0.1055; runner-up 71 at dist 0.1310)</t>
         </is>
       </c>
     </row>
@@ -1269,14 +1269,14 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0.576</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on back-skirt bones, lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:8 at dist 0.1616)</t>
+          <t>Reviewed (2026-09-25): whole outfit on the main mesh -- a cut between main mesh and Coat tore capes open in game (Neuvillette3/4/5); upper links on the PELVIS too (back-skirt bones folded Neuvillette3's flap), lower on knees/shins, 0/1 on the spine. | was: Reviewed (in game, Neuvillette3, 2026-09-24): his coat-tail chain goes WHOLE into the Coat, down its back panel by height -- split between the main mesh's back pieces and the Coat's tail ends, a vertex weighted to both was drawn by both components and the hem came out sawtoothed. (was: 209 verts (Body) -&gt; 173 verts (Head), dist 0.1485; runner-up Coat:8 at dist 0.1616)</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
+++ b/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
@@ -1333,14 +1333,14 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0.774</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>120 verts (Body) -&gt; 479 verts (Body/Head), dist 0.0977; runner-up 81 at dist 0.1163</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: 120 verts (Body) -&gt; 479 verts (Body/Head), dist 0.0977; runner-up 81 at dist 0.1163</t>
         </is>
       </c>
     </row>
@@ -1349,14 +1349,14 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0.5610000000000001</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>184 verts (Body) -&gt; 188 verts (Dress), dist 0.0944; runner-up 82 at dist 0.2087</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: 184 verts (Body) -&gt; 188 verts (Dress), dist 0.0944; runner-up 82 at dist 0.2087</t>
         </is>
       </c>
     </row>
@@ -1365,14 +1365,14 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0.471</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>178 verts (Body) -&gt; 148 verts (Dress), dist 0.1703; runner-up 84 at dist 0.2463</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: 178 verts (Body) -&gt; 148 verts (Dress), dist 0.1703; runner-up 84 at dist 0.2463</t>
         </is>
       </c>
     </row>
@@ -1381,14 +1381,14 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0.906</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Reviewed: bottom of the front coat panel chain 48-51; continues the skin's front chain (81 -&gt; 83) rather than the thigh. Tool proposed 23. (140 verts (Body) -&gt; 192 verts (Body), dist 0.2769; runner-up 6 at dist 0.2841)</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: Reviewed: bottom of the front coat panel chain 48-51; continues the skin's front chain (81 -&gt; 83) rather than the thigh. Tool proposed 23. (140 verts (Body) -&gt; 192 verts (Body), dist 0.2769; runner-up 6 at dist 0.2841)</t>
         </is>
       </c>
     </row>
@@ -1397,14 +1397,14 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0.718</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>120 verts (Body) -&gt; 440 verts (Body/Head), dist 0.0972; runner-up 82 at dist 0.1213</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: 120 verts (Body) -&gt; 440 verts (Body/Head), dist 0.0972; runner-up 82 at dist 0.1213</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1413,14 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0.44</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>184 verts (Body) -&gt; 205 verts (Dress/Head), dist 0.0893; runner-up 84 at dist 0.1248</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: 184 verts (Body) -&gt; 205 verts (Dress/Head), dist 0.0893; runner-up 84 at dist 0.1248</t>
         </is>
       </c>
     </row>
@@ -1429,14 +1429,14 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0.636</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>178 verts (Body) -&gt; 160 verts (Dress), dist 0.1740; runner-up 83 at dist 0.2445</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: 178 verts (Body) -&gt; 160 verts (Dress), dist 0.1740; runner-up 83 at dist 0.2445</t>
         </is>
       </c>
     </row>
@@ -1445,14 +1445,14 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0.906</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Reviewed: bottom of the front coat panel chain 52-55; continues the skin's front chain (82 -&gt; 84) rather than the thigh. Tool proposed 43. (140 verts (Body) -&gt; 192 verts (Body), dist 0.2769; runner-up 26 at dist 0.2841)</t>
+          <t>Reviewed (2026-09-26): front coat panel on the PELVIS like every coat link -- on the skin's front skirt chain Neuvillette3's front flap folded back over its lining. | was: Reviewed: bottom of the front coat panel chain 52-55; continues the skin's front chain (82 -&gt; 84) rather than the thigh. Tool proposed 43. (140 verts (Body) -&gt; 192 verts (Body), dist 0.2769; runner-up 26 at dist 0.2841)</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
+++ b/Data/RemapDrafts/NeuvilletteRemapDraft.xlsx
@@ -63,17 +63,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -446,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -473,9 +476,17 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>🧥🪡 The Coat Tailor: The 51st member of The Council</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
